--- a/Actividad_Normalizacion_Estacionamiento_ALAN.xlsx
+++ b/Actividad_Normalizacion_Estacionamiento_ALAN.xlsx
@@ -8,31 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanRuiz\Desktop\BASE-BASE-BASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F999AD4-FF78-4580-A4AF-8CC749402BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE7A75B-3FBC-4137-9FA9-17C1710BB93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_GUIA_ESTUDIANTE" sheetId="1" r:id="rId1"/>
     <sheet name="TICKET" sheetId="2" r:id="rId2"/>
-    <sheet name="TICKET | MEDIO DE PAGO (N-M)" sheetId="20" r:id="rId3"/>
-    <sheet name="MEDIO DE PAGO" sheetId="19" r:id="rId4"/>
-    <sheet name="ESTADO PAGO" sheetId="18" r:id="rId5"/>
-    <sheet name="ESTADO ESPACIO" sheetId="17" r:id="rId6"/>
-    <sheet name="SECTOR" sheetId="14" r:id="rId7"/>
-    <sheet name="APARCAMIENTO" sheetId="15" r:id="rId8"/>
-    <sheet name="TRABAJADOR" sheetId="11" r:id="rId9"/>
-    <sheet name="TURNO " sheetId="12" r:id="rId10"/>
-    <sheet name="TRABAJADOR | TURNO (N-M)" sheetId="13" r:id="rId11"/>
-    <sheet name="SECTOR | APARCAMIENTO (N-M)" sheetId="16" r:id="rId12"/>
-    <sheet name="CLIENTE" sheetId="8" r:id="rId13"/>
-    <sheet name="TIPO DE CLIENTE" sheetId="7" r:id="rId14"/>
+    <sheet name="TICKET | MEDIO DE PAGO (N-M)" sheetId="20" state="hidden" r:id="rId3"/>
+    <sheet name="MEDIO DE PAGO" sheetId="19" state="hidden" r:id="rId4"/>
+    <sheet name="ESTADO PAGO" sheetId="18" state="hidden" r:id="rId5"/>
+    <sheet name="ESTADO ESPACIO" sheetId="17" state="hidden" r:id="rId6"/>
+    <sheet name="SECTOR" sheetId="14" state="hidden" r:id="rId7"/>
+    <sheet name="APARCAMIENTO" sheetId="15" state="hidden" r:id="rId8"/>
+    <sheet name="TRABAJADOR" sheetId="11" state="hidden" r:id="rId9"/>
+    <sheet name="TURNO " sheetId="12" state="hidden" r:id="rId10"/>
+    <sheet name="TRABAJADOR | TURNO (N-M)" sheetId="13" state="hidden" r:id="rId11"/>
+    <sheet name="SECTOR | APARCAMIENTO (N-M)" sheetId="16" state="hidden" r:id="rId12"/>
+    <sheet name="CLIENTE" sheetId="8" state="hidden" r:id="rId13"/>
+    <sheet name="TIPO DE CLIENTE" sheetId="7" state="hidden" r:id="rId14"/>
     <sheet name="VEHÍCULO" sheetId="9" r:id="rId15"/>
-    <sheet name="MARCAS" sheetId="4" r:id="rId16"/>
-    <sheet name="MODELO" sheetId="10" r:id="rId17"/>
-    <sheet name="COLOR" sheetId="5" r:id="rId18"/>
+    <sheet name="MARCAS" sheetId="4" state="hidden" r:id="rId16"/>
+    <sheet name="MODELO" sheetId="10" state="hidden" r:id="rId17"/>
+    <sheet name="COLOR" sheetId="5" state="hidden" r:id="rId18"/>
     <sheet name="TIPO DE VEHÍCULO" sheetId="6" r:id="rId19"/>
-    <sheet name="99_PAUTA_DOCENTE" sheetId="3" r:id="rId20"/>
+    <sheet name="99_PAUTA_DOCENTE" sheetId="3" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TICKET!$A$1:$AA$61</definedName>
@@ -143,23 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>======
-ID#AAACGQhMUbE
-Actividad    (2026-08-31 03:02:03)
-¿La tarifa pertenece a la estadía o a otra entidad? ¿Qué ocurre si cambia la tarifa?</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{663706C8-9F1B-4A9C-B9A2-3530CF841A98}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{BCD55820-0101-46BB-AA9F-78C63AE6D48D}">
       <text>
         <r>
           <rPr>
@@ -289,9 +273,6 @@
     <t>3. Determina qué columnas podrían funcionar como identificadores únicos.</t>
   </si>
   <si>
-    <t>Tarifa Aplicada</t>
-  </si>
-  <si>
     <t>4. Busca datos que deberían mantenerse consistentes, pero aparecen escritos de distintas maneras.</t>
   </si>
   <si>
@@ -1265,6 +1246,9 @@
   </si>
   <si>
     <t>ID_medio_de_pago</t>
+  </si>
+  <si>
+    <t>Tarifa</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1683,6 +1667,7 @@
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1963,22 +1948,22 @@
     </row>
     <row r="13" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,42 +1971,42 @@
     </row>
     <row r="18" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2029,27 +2014,27 @@
     </row>
     <row r="27" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2057,22 +2042,22 @@
     </row>
     <row r="33" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3052,7 +3037,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="30" t="s">
         <v>10</v>
@@ -3063,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3071,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3079,7 +3064,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3087,7 +3072,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -3105,10 +3090,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>299</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,10 +3143,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>334</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3345,22 +3330,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3368,16 +3353,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>921234567</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3388,16 +3373,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3">
         <v>945678123</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -3408,16 +3393,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>912345678</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -3428,16 +3413,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5">
         <v>987123456</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -3448,16 +3433,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6">
         <v>934567890</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -3468,16 +3453,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7">
         <v>956789012</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -3488,16 +3473,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8">
         <v>987654321</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -3508,16 +3493,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9">
         <v>976543210</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -3528,16 +3513,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D10">
         <v>998765432</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -3548,16 +3533,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D11">
         <v>923456789</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -3578,10 +3563,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3589,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3597,7 +3582,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3617,25 +3602,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="16" t="s">
-        <v>289</v>
-      </c>
       <c r="E1" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F1" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>294</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3643,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3666,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -3689,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -3712,7 +3697,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -3735,7 +3720,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -3758,7 +3743,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -3781,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -3804,7 +3789,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3827,7 +3812,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -3850,7 +3835,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -3873,7 +3858,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3896,7 +3881,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -3916,6 +3901,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3929,10 +3915,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3940,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3948,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3956,7 +3942,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3964,7 +3950,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3972,7 +3958,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3980,7 +3966,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3988,7 +3974,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3996,7 +3982,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4171,10 +4157,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4190,7 +4176,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4198,7 +4184,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4206,7 +4192,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4214,7 +4200,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4222,7 +4208,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4230,7 +4216,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4238,7 +4224,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4232,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4254,7 +4240,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4262,7 +4248,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4270,7 +4256,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4278,7 +4264,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4286,7 +4272,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4439,7 +4425,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>5</v>
@@ -4450,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4458,7 +4444,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4466,7 +4452,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4474,7 +4460,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4482,7 +4468,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4490,7 +4476,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4498,7 +4484,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4506,7 +4492,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4514,7 +4500,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4522,7 +4508,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4530,7 +4516,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -4540,46 +4526,59 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2665C941-3753-4634-A1E5-1A2BCD5371C0}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="C3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
+      </c>
+      <c r="C4">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4597,8 +4596,8 @@
     <col min="9" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="25.140625" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
@@ -4627,38 +4626,36 @@
         <v>4</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G1" s="38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I1" s="23" t="s">
         <v>12</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="37" t="s">
-        <v>27</v>
-      </c>
+      <c r="L1" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="47"/>
       <c r="P1" s="47"/>
       <c r="Q1" s="45"/>
       <c r="R1" s="45"/>
@@ -4675,13 +4672,13 @@
         <v>10401</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="9">
         <v>1</v>
@@ -4705,14 +4702,12 @@
         <v>2</v>
       </c>
       <c r="L2" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M2" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N2" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -4730,13 +4725,13 @@
         <v>10402</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="E3" s="9">
         <v>2</v>
@@ -4760,14 +4755,12 @@
         <v>5</v>
       </c>
       <c r="L3" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M3" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -4785,13 +4778,13 @@
         <v>10403</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="E4" s="9">
         <v>3</v>
@@ -4815,14 +4808,12 @@
         <v>3</v>
       </c>
       <c r="L4" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M4" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N4" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -4840,13 +4831,13 @@
         <v>10404</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="E5" s="9">
         <v>4</v>
@@ -4870,17 +4861,15 @@
         <v>2</v>
       </c>
       <c r="L5" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M5" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N5" s="4">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -4897,13 +4886,13 @@
         <v>10405</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="E6" s="9">
         <v>5</v>
@@ -4927,17 +4916,15 @@
         <v>5</v>
       </c>
       <c r="L6" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M6" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N6" s="4">
-        <v>1</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -4954,13 +4941,13 @@
         <v>10406</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="E7" s="4">
         <v>5</v>
@@ -4987,14 +4974,12 @@
         <v>1500</v>
       </c>
       <c r="M7" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N7" s="4">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
@@ -5011,13 +4996,13 @@
         <v>10407</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="E8" s="9">
         <v>6</v>
@@ -5041,17 +5026,15 @@
         <v>4</v>
       </c>
       <c r="L8" s="4">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="M8" s="4">
-        <v>8000</v>
-      </c>
-      <c r="N8" s="4">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -5068,13 +5051,13 @@
         <v>10408</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="E9" s="9">
         <v>7</v>
@@ -5101,11 +5084,9 @@
         <v>1500</v>
       </c>
       <c r="M9" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -5123,13 +5104,13 @@
         <v>10409</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E10" s="4">
         <v>3</v>
@@ -5153,17 +5134,15 @@
         <v>3</v>
       </c>
       <c r="L10" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M10" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N10" s="4">
-        <v>1</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -5180,13 +5159,13 @@
         <v>10410</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="E11" s="9">
         <v>8</v>
@@ -5210,17 +5189,15 @@
         <v>3</v>
       </c>
       <c r="L11" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M11" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N11" s="4">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -5237,13 +5214,13 @@
         <v>10411</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="E12" s="9">
         <v>9</v>
@@ -5267,17 +5244,15 @@
         <v>3</v>
       </c>
       <c r="L12" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M12" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N12" s="4">
-        <v>1</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -5294,13 +5269,13 @@
         <v>10412</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="E13" s="4">
         <v>4</v>
@@ -5324,14 +5299,12 @@
         <v>5</v>
       </c>
       <c r="L13" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M13" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N13" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -5349,13 +5322,13 @@
         <v>10413</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="E14" s="4">
         <v>8</v>
@@ -5382,14 +5355,12 @@
         <v>1500</v>
       </c>
       <c r="M14" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N14" s="4">
-        <v>1</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -5406,13 +5377,13 @@
         <v>10414</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -5436,17 +5407,15 @@
         <v>2</v>
       </c>
       <c r="L15" s="4">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="M15" s="4">
-        <v>3600</v>
-      </c>
-      <c r="N15" s="4">
-        <v>1</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -5463,13 +5432,13 @@
         <v>10415</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="E16" s="4">
         <v>1</v>
@@ -5496,14 +5465,12 @@
         <v>1500</v>
       </c>
       <c r="M16" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N16" s="4">
-        <v>1</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -5520,13 +5487,13 @@
         <v>10416</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="4">
         <v>3</v>
@@ -5550,17 +5517,15 @@
         <v>5</v>
       </c>
       <c r="L17" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M17" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N17" s="4">
-        <v>1</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -5577,13 +5542,13 @@
         <v>10417</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="E18" s="4">
         <v>12</v>
@@ -5610,14 +5575,12 @@
         <v>1800</v>
       </c>
       <c r="M18" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N18" s="4">
-        <v>1</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -5634,13 +5597,13 @@
         <v>10418</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="E19" s="4">
         <v>6</v>
@@ -5664,14 +5627,12 @@
         <v>5</v>
       </c>
       <c r="L19" s="4">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="M19" s="4">
-        <v>10000</v>
-      </c>
-      <c r="N19" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -5689,13 +5650,13 @@
         <v>10419</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>192</v>
       </c>
       <c r="E20" s="4">
         <v>12</v>
@@ -5709,7 +5670,7 @@
       <c r="H20" s="4">
         <v>3</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="9">
         <v>2</v>
       </c>
       <c r="J20" s="4">
@@ -5719,17 +5680,15 @@
         <v>4</v>
       </c>
       <c r="L20" s="4">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="M20" s="4">
-        <v>7200</v>
-      </c>
-      <c r="N20" s="4">
-        <v>1</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
@@ -5746,13 +5705,13 @@
         <v>10420</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="E21" s="4">
         <v>4</v>
@@ -5776,17 +5735,15 @@
         <v>2</v>
       </c>
       <c r="L21" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M21" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N21" s="4">
-        <v>1</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
@@ -5803,13 +5760,13 @@
         <v>10421</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="E22" s="4">
         <v>5</v>
@@ -5836,11 +5793,9 @@
         <v>1500</v>
       </c>
       <c r="M22" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N22" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
@@ -5858,13 +5813,13 @@
         <v>10422</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="E23" s="4">
         <v>9</v>
@@ -5888,17 +5843,15 @@
         <v>3</v>
       </c>
       <c r="L23" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M23" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N23" s="4">
-        <v>1</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
@@ -5915,13 +5868,13 @@
         <v>10423</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="E24" s="4">
         <v>9</v>
@@ -5945,14 +5898,12 @@
         <v>4</v>
       </c>
       <c r="L24" s="4">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M24" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N24" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N24" s="4"/>
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
@@ -5970,13 +5921,13 @@
         <v>10424</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>204</v>
       </c>
       <c r="E25" s="4">
         <v>5</v>
@@ -6003,11 +5954,9 @@
         <v>1500</v>
       </c>
       <c r="M25" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N25" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N25" s="4"/>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
@@ -6025,13 +5974,13 @@
         <v>10425</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E26" s="4">
         <v>8</v>
@@ -6055,17 +6004,15 @@
         <v>2</v>
       </c>
       <c r="L26" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M26" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N26" s="4">
-        <v>1</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
@@ -6082,13 +6029,13 @@
         <v>10426</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="E27" s="4">
         <v>12</v>
@@ -6112,14 +6059,12 @@
         <v>5</v>
       </c>
       <c r="L27" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M27" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N27" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N27" s="4"/>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
@@ -6137,13 +6082,13 @@
         <v>10427</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="E28" s="4">
         <v>8</v>
@@ -6167,17 +6112,15 @@
         <v>5</v>
       </c>
       <c r="L28" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M28" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N28" s="4">
-        <v>1</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
@@ -6194,13 +6137,13 @@
         <v>10428</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E29" s="4">
         <v>8</v>
@@ -6224,17 +6167,15 @@
         <v>3</v>
       </c>
       <c r="L29" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M29" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N29" s="4">
-        <v>1</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
@@ -6251,13 +6192,13 @@
         <v>10429</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="E30" s="4">
         <v>12</v>
@@ -6281,17 +6222,15 @@
         <v>5</v>
       </c>
       <c r="L30" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M30" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N30" s="4">
-        <v>1</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
@@ -6308,13 +6247,13 @@
         <v>10430</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="E31" s="4">
         <v>8</v>
@@ -6338,14 +6277,12 @@
         <v>2</v>
       </c>
       <c r="L31" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M31" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N31" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N31" s="4"/>
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
@@ -6363,13 +6300,13 @@
         <v>10431</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="E32" s="4">
         <v>12</v>
@@ -6393,17 +6330,15 @@
         <v>4</v>
       </c>
       <c r="L32" s="4">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="M32" s="4">
-        <v>7200</v>
-      </c>
-      <c r="N32" s="4">
-        <v>1</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
@@ -6420,13 +6355,13 @@
         <v>10432</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
@@ -6450,17 +6385,15 @@
         <v>5</v>
       </c>
       <c r="L33" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M33" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N33" s="4">
-        <v>1</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
@@ -6477,13 +6410,13 @@
         <v>10433</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="E34" s="4">
         <v>9</v>
@@ -6507,17 +6440,15 @@
         <v>3</v>
       </c>
       <c r="L34" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M34" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N34" s="4">
-        <v>1</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O34" s="4"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
@@ -6534,13 +6465,13 @@
         <v>10434</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E35" s="4">
         <v>5</v>
@@ -6564,14 +6495,12 @@
         <v>5</v>
       </c>
       <c r="L35" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M35" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N35" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
@@ -6589,13 +6518,13 @@
         <v>10435</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E36" s="4">
         <v>7</v>
@@ -6619,17 +6548,15 @@
         <v>5</v>
       </c>
       <c r="L36" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M36" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N36" s="4">
-        <v>1</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O36" s="4"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
@@ -6646,13 +6573,13 @@
         <v>10436</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="E37" s="4">
         <v>2</v>
@@ -6676,14 +6603,12 @@
         <v>3</v>
       </c>
       <c r="L37" s="4">
-        <v>1800</v>
+        <v>5400</v>
       </c>
       <c r="M37" s="4">
-        <v>5400</v>
-      </c>
-      <c r="N37" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
@@ -6701,13 +6626,13 @@
         <v>10437</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="D38" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E38" s="4">
         <v>4</v>
@@ -6731,17 +6656,15 @@
         <v>4</v>
       </c>
       <c r="L38" s="4">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M38" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N38" s="4">
-        <v>1</v>
-      </c>
-      <c r="O38" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O38" s="4"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -6758,13 +6681,13 @@
         <v>10438</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="E39" s="4">
         <v>3</v>
@@ -6788,14 +6711,12 @@
         <v>3</v>
       </c>
       <c r="L39" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M39" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N39" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
@@ -6813,13 +6734,13 @@
         <v>10439</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E40" s="4">
         <v>7</v>
@@ -6843,14 +6764,12 @@
         <v>4</v>
       </c>
       <c r="L40" s="4">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M40" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N40" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N40" s="4"/>
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
@@ -6868,13 +6787,13 @@
         <v>10440</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="E41" s="4">
         <v>5</v>
@@ -6898,14 +6817,12 @@
         <v>2</v>
       </c>
       <c r="L41" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M41" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N41" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N41" s="4"/>
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
@@ -6923,13 +6840,13 @@
         <v>10441</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="E42" s="4">
         <v>8</v>
@@ -6953,14 +6870,12 @@
         <v>3</v>
       </c>
       <c r="L42" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M42" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N42" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
@@ -6978,13 +6893,13 @@
         <v>10442</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="E43" s="4">
         <v>7</v>
@@ -7008,14 +6923,12 @@
         <v>2</v>
       </c>
       <c r="L43" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M43" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N43" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
@@ -7033,13 +6946,13 @@
         <v>10443</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E44" s="4">
         <v>12</v>
@@ -7063,14 +6976,12 @@
         <v>2</v>
       </c>
       <c r="L44" s="4">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="M44" s="4">
-        <v>3600</v>
-      </c>
-      <c r="N44" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
@@ -7088,13 +6999,13 @@
         <v>10444</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="E45" s="4">
         <v>10</v>
@@ -7118,17 +7029,15 @@
         <v>3</v>
       </c>
       <c r="L45" s="4">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="M45" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N45" s="4">
-        <v>1</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O45" s="4"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
@@ -7145,13 +7054,13 @@
         <v>10445</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E46" s="4">
         <v>11</v>
@@ -7175,17 +7084,15 @@
         <v>5</v>
       </c>
       <c r="L46" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M46" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N46" s="4">
-        <v>1</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O46" s="4"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
@@ -7202,13 +7109,13 @@
         <v>10446</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="E47" s="4">
         <v>8</v>
@@ -7232,17 +7139,15 @@
         <v>2</v>
       </c>
       <c r="L47" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M47" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N47" s="4">
-        <v>1</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O47" s="4"/>
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
@@ -7259,13 +7164,13 @@
         <v>10447</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="E48" s="4">
         <v>7</v>
@@ -7289,17 +7194,15 @@
         <v>3</v>
       </c>
       <c r="L48" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M48" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N48" s="4">
-        <v>1</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O48" s="4"/>
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
@@ -7316,13 +7219,13 @@
         <v>10448</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="E49" s="4">
         <v>8</v>
@@ -7346,14 +7249,12 @@
         <v>3</v>
       </c>
       <c r="L49" s="4">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="M49" s="4">
-        <v>4500</v>
-      </c>
-      <c r="N49" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
@@ -7371,13 +7272,13 @@
         <v>10449</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="E50" s="4">
         <v>4</v>
@@ -7401,17 +7302,15 @@
         <v>4</v>
       </c>
       <c r="L50" s="4">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M50" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N50" s="4">
-        <v>1</v>
-      </c>
-      <c r="O50" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O50" s="4"/>
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
@@ -7428,13 +7327,13 @@
         <v>10450</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C51" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="E51" s="4">
         <v>3</v>
@@ -7458,17 +7357,15 @@
         <v>2</v>
       </c>
       <c r="L51" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M51" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N51" s="4">
-        <v>1</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O51" s="4"/>
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
@@ -7485,13 +7382,13 @@
         <v>10451</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E52" s="4">
         <v>11</v>
@@ -7515,17 +7412,15 @@
         <v>4</v>
       </c>
       <c r="L52" s="4">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="M52" s="4">
-        <v>7200</v>
-      </c>
-      <c r="N52" s="4">
-        <v>1</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O52" s="4"/>
       <c r="P52" s="4"/>
       <c r="Q52" s="9"/>
       <c r="R52" s="4"/>
@@ -7542,13 +7437,13 @@
         <v>10452</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E53" s="4">
         <v>10</v>
@@ -7572,17 +7467,15 @@
         <v>2</v>
       </c>
       <c r="L53" s="4">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M53" s="4">
-        <v>4000</v>
-      </c>
-      <c r="N53" s="4">
-        <v>1</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O53" s="4"/>
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
@@ -7599,13 +7492,13 @@
         <v>10453</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="E54" s="4">
         <v>5</v>
@@ -7629,14 +7522,12 @@
         <v>2</v>
       </c>
       <c r="L54" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M54" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N54" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
       <c r="Q54" s="9"/>
@@ -7654,13 +7545,13 @@
         <v>10454</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E55" s="4">
         <v>9</v>
@@ -7684,17 +7575,15 @@
         <v>2</v>
       </c>
       <c r="L55" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M55" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N55" s="4">
-        <v>1</v>
-      </c>
-      <c r="O55" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O55" s="4"/>
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
@@ -7711,13 +7600,13 @@
         <v>10455</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C56" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="E56" s="4">
         <v>10</v>
@@ -7741,17 +7630,15 @@
         <v>2</v>
       </c>
       <c r="L56" s="4">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M56" s="4">
-        <v>4000</v>
-      </c>
-      <c r="N56" s="4">
-        <v>1</v>
-      </c>
-      <c r="O56" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O56" s="4"/>
       <c r="P56" s="4"/>
       <c r="Q56" s="9"/>
       <c r="R56" s="4"/>
@@ -7768,13 +7655,13 @@
         <v>10456</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E57" s="4">
         <v>12</v>
@@ -7798,17 +7685,15 @@
         <v>5</v>
       </c>
       <c r="L57" s="4">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="M57" s="4">
-        <v>9000</v>
-      </c>
-      <c r="N57" s="4">
-        <v>1</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O57" s="4"/>
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
@@ -7825,13 +7710,13 @@
         <v>10457</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E58" s="4">
         <v>10</v>
@@ -7855,17 +7740,15 @@
         <v>5</v>
       </c>
       <c r="L58" s="4">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="M58" s="4">
-        <v>10000</v>
-      </c>
-      <c r="N58" s="4">
-        <v>1</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O58" s="4"/>
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
@@ -7882,13 +7765,13 @@
         <v>10458</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="E59" s="4">
         <v>1</v>
@@ -7912,17 +7795,15 @@
         <v>5</v>
       </c>
       <c r="L59" s="4">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="M59" s="4">
-        <v>7500</v>
-      </c>
-      <c r="N59" s="4">
-        <v>1</v>
-      </c>
-      <c r="O59" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O59" s="4"/>
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
@@ -7939,13 +7820,13 @@
         <v>10459</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E60" s="4">
         <v>9</v>
@@ -7969,17 +7850,15 @@
         <v>2</v>
       </c>
       <c r="L60" s="4">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="M60" s="4">
-        <v>3000</v>
-      </c>
-      <c r="N60" s="4">
-        <v>1</v>
-      </c>
-      <c r="O60" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O60" s="4"/>
       <c r="P60" s="4"/>
       <c r="Q60" s="9"/>
       <c r="R60" s="4"/>
@@ -7996,13 +7875,13 @@
         <v>10460</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="E61" s="4">
         <v>4</v>
@@ -8026,17 +7905,15 @@
         <v>4</v>
       </c>
       <c r="L61" s="4">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M61" s="4">
-        <v>6000</v>
-      </c>
-      <c r="N61" s="4">
-        <v>1</v>
-      </c>
-      <c r="O61" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O61" s="4"/>
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
@@ -9010,80 +8887,80 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10082,10 +9959,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10592,10 +10469,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10603,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -10611,7 +10488,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10619,7 +10496,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -10637,10 +10514,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10648,7 +10525,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -10656,7 +10533,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10664,7 +10541,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -10682,10 +10559,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10693,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -10701,7 +10578,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -10716,10 +10593,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10727,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -10735,7 +10612,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10743,7 +10620,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -10761,10 +10638,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -10772,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -10780,7 +10657,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10788,7 +10665,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -10796,7 +10673,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -10804,7 +10681,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -10812,7 +10689,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -10820,7 +10697,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -10828,7 +10705,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -10836,7 +10713,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -10844,7 +10721,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -10852,7 +10729,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -10860,7 +10737,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -10868,7 +10745,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -10876,7 +10753,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -10884,7 +10761,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -10892,7 +10769,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -10900,7 +10777,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -10908,7 +10785,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -10916,7 +10793,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -10924,7 +10801,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -10932,7 +10809,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -10940,7 +10817,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -10948,7 +10825,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -10956,7 +10833,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -10964,7 +10841,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -10972,7 +10849,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -10980,7 +10857,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -10988,7 +10865,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -10996,7 +10873,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -11004,7 +10881,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -11024,13 +10901,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B1" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>282</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11038,10 +10915,10 @@
         <v>201</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -11049,10 +10926,10 @@
         <v>202</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>103</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -11060,10 +10937,10 @@
         <v>203</v>
       </c>
       <c r="B4" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>125</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -11071,10 +10948,10 @@
         <v>204</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
